--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4210" uniqueCount="2796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4249" uniqueCount="2822">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-01-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1249,7 +1249,7 @@
     <t>0182</t>
   </si>
   <si>
-    <t>Education thérapeutique - école de l'asthme</t>
+    <t>Education thérapeutique labellisée du patient asthmatique (école de l'asthme)</t>
   </si>
   <si>
     <t>0183</t>
@@ -3163,7 +3163,7 @@
     <t>0501</t>
   </si>
   <si>
-    <t>Vaccination internationale, conseil aux voyageurs (fièvre jaune, encéphalite...)</t>
+    <t>Vaccinations internationales et conseils aux voyageurs</t>
   </si>
   <si>
     <t>0502</t>
@@ -8371,7 +8371,7 @@
     <t>1381</t>
   </si>
   <si>
-    <t>Diagnostic complexe de l'endométriose</t>
+    <t>Diagnostic de l'endométriose complexe</t>
   </si>
   <si>
     <t>1382</t>
@@ -8402,6 +8402,84 @@
   </si>
   <si>
     <t>Suivi psychiatrique de la femme enceinte</t>
+  </si>
+  <si>
+    <t>1387</t>
+  </si>
+  <si>
+    <t>Conseil en anti infectieux</t>
+  </si>
+  <si>
+    <t>1388</t>
+  </si>
+  <si>
+    <t>Gestion des complications de l'infection par le VIH</t>
+  </si>
+  <si>
+    <t>1389</t>
+  </si>
+  <si>
+    <t>Initiation et suivi thérapeutique des hépatites virales</t>
+  </si>
+  <si>
+    <t>1390</t>
+  </si>
+  <si>
+    <t>Initiation, réévaluation et modification des anti rétroviraux</t>
+  </si>
+  <si>
+    <t>1391</t>
+  </si>
+  <si>
+    <t>Maladies vectorielles à tique (Lyme…)</t>
+  </si>
+  <si>
+    <t>1392</t>
+  </si>
+  <si>
+    <t>Prise en charge clinique des parasitoses</t>
+  </si>
+  <si>
+    <t>1393</t>
+  </si>
+  <si>
+    <t>Prise en charge des Infections chez les Immunodéprimés (ID)</t>
+  </si>
+  <si>
+    <t>1394</t>
+  </si>
+  <si>
+    <t>PEC diag et thérapeutique infections post-opé, sur prothèses, disp implantables</t>
+  </si>
+  <si>
+    <t>1395</t>
+  </si>
+  <si>
+    <t>Bilan diagnostic psychiatrique</t>
+  </si>
+  <si>
+    <t>1396</t>
+  </si>
+  <si>
+    <t>Prise en charge de l'anorexie précoce prépubère</t>
+  </si>
+  <si>
+    <t>1397</t>
+  </si>
+  <si>
+    <t>Prise en charge de l'hyperphagie boulimique</t>
+  </si>
+  <si>
+    <t>1398</t>
+  </si>
+  <si>
+    <t>Admission directe non programmée - PA</t>
+  </si>
+  <si>
+    <t>1399</t>
+  </si>
+  <si>
+    <t>Unité de réanimation pédiatrique de recours</t>
   </si>
 </sst>
 </file>
@@ -8767,7 +8845,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1387"/>
+  <dimension ref="A1:D1400"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -25416,6 +25494,162 @@
       </c>
       <c r="D1387" s="2"/>
     </row>
+    <row r="1388">
+      <c r="A1388" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1388" t="s" s="2">
+        <v>2796</v>
+      </c>
+      <c r="C1388" t="s" s="2">
+        <v>2797</v>
+      </c>
+      <c r="D1388" s="2"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1389" t="s" s="2">
+        <v>2798</v>
+      </c>
+      <c r="C1389" t="s" s="2">
+        <v>2799</v>
+      </c>
+      <c r="D1389" s="2"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1390" t="s" s="2">
+        <v>2800</v>
+      </c>
+      <c r="C1390" t="s" s="2">
+        <v>2801</v>
+      </c>
+      <c r="D1390" s="2"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1391" t="s" s="2">
+        <v>2802</v>
+      </c>
+      <c r="C1391" t="s" s="2">
+        <v>2803</v>
+      </c>
+      <c r="D1391" s="2"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1392" t="s" s="2">
+        <v>2804</v>
+      </c>
+      <c r="C1392" t="s" s="2">
+        <v>2805</v>
+      </c>
+      <c r="D1392" s="2"/>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1393" t="s" s="2">
+        <v>2806</v>
+      </c>
+      <c r="C1393" t="s" s="2">
+        <v>2807</v>
+      </c>
+      <c r="D1393" s="2"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1394" t="s" s="2">
+        <v>2808</v>
+      </c>
+      <c r="C1394" t="s" s="2">
+        <v>2809</v>
+      </c>
+      <c r="D1394" s="2"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1395" t="s" s="2">
+        <v>2810</v>
+      </c>
+      <c r="C1395" t="s" s="2">
+        <v>2811</v>
+      </c>
+      <c r="D1395" s="2"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1396" t="s" s="2">
+        <v>2812</v>
+      </c>
+      <c r="C1396" t="s" s="2">
+        <v>2813</v>
+      </c>
+      <c r="D1396" s="2"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1397" t="s" s="2">
+        <v>2814</v>
+      </c>
+      <c r="C1397" t="s" s="2">
+        <v>2815</v>
+      </c>
+      <c r="D1397" s="2"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1398" t="s" s="2">
+        <v>2816</v>
+      </c>
+      <c r="C1398" t="s" s="2">
+        <v>2817</v>
+      </c>
+      <c r="D1398" s="2"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1399" t="s" s="2">
+        <v>2818</v>
+      </c>
+      <c r="C1399" t="s" s="2">
+        <v>2819</v>
+      </c>
+      <c r="D1399" s="2"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B1400" t="s" s="2">
+        <v>2820</v>
+      </c>
+      <c r="C1400" t="s" s="2">
+        <v>2821</v>
+      </c>
+      <c r="D1400" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>id: Uniform Resource Identifier (URI)#urn:oid:1.2.250.1.213.3.3.11</t>
+    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#urn:oid:1.2.250.1.213.3.3.11</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#urn:oid:1.2.250.1.213.3.3.11</t>
+    <t>OID:1.2.250.1.213.3.3.11</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -76,7 +76,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4556" uniqueCount="3100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4663" uniqueCount="3174">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T12:00:00+01:00</t>
+    <t>2024-06-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4963,7 +4963,7 @@
     <t>0776</t>
   </si>
   <si>
-    <t>Accompagnement aux pratiques numériques</t>
+    <t>Accompagnement aux pratiques numériques et assistance informatique</t>
   </si>
   <si>
     <t>0777</t>
@@ -8806,7 +8806,7 @@
     <t>1354</t>
   </si>
   <si>
-    <t>PEC en ACT en hébergement collectif</t>
+    <t>Prise en charge en Appartements de Coordination Thérapeutique (ACT) partagé</t>
   </si>
   <si>
     <t>Prise en charge, comprenant des soins médicaux, psychologiques ou sociaux et un suivi régulier, de résidents hébergés dans des logements réunis à une adresse commune.</t>
@@ -8815,7 +8815,7 @@
     <t>1355</t>
   </si>
   <si>
-    <t>PEC en ACT en appartements en diffus</t>
+    <t>Prise en charge en Appartements de Coordination Thérapeutique (ACT) individuel</t>
   </si>
   <si>
     <t>Prise en charge comprenant des soins médicaux, psychologiques ou sociaux et un suivi régulier, de résidents hébergés dans différents bâtiments répartis dans la ville.</t>
@@ -9160,12 +9160,18 @@
     <t>Accueil et prise en charge du polytraumatisé sévère</t>
   </si>
   <si>
+    <t>Structure équipée et dotée en personnel pour permettre une chaîne de soins structurée faisant intervenir le plus rapidement possible de nombreuses spécialités médicales et chirurgicales, pour prodiguer des soins aux patients souffrant de blessures traumatiques graves telles que des chutes, des collisions de véhicules à moteur ou des blessures par balle.</t>
+  </si>
+  <si>
     <t>1401</t>
   </si>
   <si>
     <t>Algologie périopératoire</t>
   </si>
   <si>
+    <t>Prise en charges des causes et le traitement de la douleur durant la période entourant un acte chirurgical ou interventionnel.</t>
+  </si>
+  <si>
     <t>1402</t>
   </si>
   <si>
@@ -9184,6 +9190,9 @@
     <t>Assistance circulatoire extracorporelle par ECMO</t>
   </si>
   <si>
+    <t>Pompe permettant d'assurer des débits sanguins extracorporels au travers d'un oxygénateur assurant les échanges gazeux. C'est une technique dérivée de la circulation extracorporelle, le sang est prélevé et renvoyé au patient à l'aide de canules vasculaires de très gros calibre, positionnées sur des axes vasculaires majeurs (fémorales, jugulaires).</t>
+  </si>
+  <si>
     <t>1405</t>
   </si>
   <si>
@@ -9214,6 +9223,9 @@
     <t>Centre labellisé Covid-Long</t>
   </si>
   <si>
+    <t>Structure reconnue et labellisée dont la mission est de diagnostiquer, établir un plan de soins personnalisé, orienter les patients et s'assurer de la mise en oeuvre effective du plan de soins, pour le patient souffrant d'un COVID long, cette prise en charge s'opèrera après orientation par la médecine de ville ou un autre service hospitalier.</t>
+  </si>
+  <si>
     <t>1410</t>
   </si>
   <si>
@@ -9292,18 +9304,27 @@
     <t>Récupération améliorée après chirurgie (RAAC) orthopédique</t>
   </si>
   <si>
+    <t>Ensemble de mesures (avant, pendant et après une intervention chirurgicale) visant à minimiser le traumatisme subi par le patient et donc accélérer sa récupération à la fois sur le plan général et sur le membre opéré : c'est donc une approche de prise en charge globale du patient favorisant le rétablissement précoce de ses capacités après la chirurgie orthopédique</t>
+  </si>
+  <si>
     <t>1423</t>
   </si>
   <si>
     <t>Récupération améliorée après chirurgie (RAAC) digestive</t>
   </si>
   <si>
+    <t>Ensemble de mesures (avant, pendant et après une intervention chirurgicale) visant à minimiser le traumatisme subi par le patient et donc accélérer sa récupération à la fois sur le plan général et sur la fonction opérée : c'est donc une approche de prise en charge globale du patient favorisant le rétablissement précoce de ses capacités après la chirurgie digestive lourde</t>
+  </si>
+  <si>
     <t>1424</t>
   </si>
   <si>
     <t>Récupération améliorée après chirurgie (RAAC) gynécologique</t>
   </si>
   <si>
+    <t>Ensemble de mesures (avant, pendant et après une intervention chirurgicale) visant à minimiser le traumatisme subi par le patient et donc accélérer sa récupération à la fois sur le plan général et sur la fonction opérée : c'est donc une approche de prise en charge globale du patient favorisant le rétablissement précoce de ses capacités après la chirurgie gynécologique lourde</t>
+  </si>
+  <si>
     <t>1425</t>
   </si>
   <si>
@@ -9314,6 +9335,207 @@
   </si>
   <si>
     <t>Traitement du psychotraumatisme</t>
+  </si>
+  <si>
+    <t>Prise en charge et le traitement de l'ensemble des troubles psychiques (reviviscences envahissantes, souffrance morale, etc.) qui peuvent survenir chez une victime dans les suites d'une exposition à un évènement traumatique (accidents graves, violences, catastrophes, etc.).</t>
+  </si>
+  <si>
+    <t>1427</t>
+  </si>
+  <si>
+    <t>Recherche d'ADN foetal libre</t>
+  </si>
+  <si>
+    <t>1428</t>
+  </si>
+  <si>
+    <t>Centre de réhabilitation psychosociale - Centre de recours labellisé</t>
+  </si>
+  <si>
+    <t>1429</t>
+  </si>
+  <si>
+    <t>Centre de réhabilitation psychosociale - Centre de proximité labellisé</t>
+  </si>
+  <si>
+    <t>1430</t>
+  </si>
+  <si>
+    <t>Accompagnement à l'éducation de l'enfant sans violence éducative ordinaire (VEO)</t>
+  </si>
+  <si>
+    <t>1431</t>
+  </si>
+  <si>
+    <t>Accompagnement d'un patient pour téléconsultation médicale</t>
+  </si>
+  <si>
+    <t>1432</t>
+  </si>
+  <si>
+    <t>Appui à l'accueil inclusif (référent)</t>
+  </si>
+  <si>
+    <t>1433</t>
+  </si>
+  <si>
+    <t>Evaluation infirmière gériatrique multidimensionnelle</t>
+  </si>
+  <si>
+    <t>1434</t>
+  </si>
+  <si>
+    <t>Guidance parentale (psychoéducation)</t>
+  </si>
+  <si>
+    <t>1435</t>
+  </si>
+  <si>
+    <t>Index de pression systolique (IPS)</t>
+  </si>
+  <si>
+    <t>1436</t>
+  </si>
+  <si>
+    <t>Rédaction de certificat de décès</t>
+  </si>
+  <si>
+    <t>1437</t>
+  </si>
+  <si>
+    <t>Réalisation de "Mon bilan prévention"</t>
+  </si>
+  <si>
+    <t>1438</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière de récupération améliorée après chirurgie (RAAC)</t>
+  </si>
+  <si>
+    <t>1439</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière des douleurs chroniques</t>
+  </si>
+  <si>
+    <t>1440</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière des maladies psychiatriques</t>
+  </si>
+  <si>
+    <t>1441</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière des pathologies cardiaques</t>
+  </si>
+  <si>
+    <t>1442</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière des pathologies respiratoires</t>
+  </si>
+  <si>
+    <t>1443</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière des soins palliatifs</t>
+  </si>
+  <si>
+    <t>1444</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière des troubles vésico-sphinctériens (TVS)</t>
+  </si>
+  <si>
+    <t>1445</t>
+  </si>
+  <si>
+    <t>Prise en charge infirmière du diabète</t>
+  </si>
+  <si>
+    <t>1446</t>
+  </si>
+  <si>
+    <t>Référent santé et accueil inclusif des établissements d'accueil du jeune enfant</t>
+  </si>
+  <si>
+    <t>1447</t>
+  </si>
+  <si>
+    <t>Prescription de vaccination</t>
+  </si>
+  <si>
+    <t>1448</t>
+  </si>
+  <si>
+    <t>Santé environnementale</t>
+  </si>
+  <si>
+    <t>1450</t>
+  </si>
+  <si>
+    <t>Soins infirmiers de dialyse péritonéale</t>
+  </si>
+  <si>
+    <t>1451</t>
+  </si>
+  <si>
+    <t>Accompagnement à la transition, au changement d'environnement, au deuil</t>
+  </si>
+  <si>
+    <t>1452</t>
+  </si>
+  <si>
+    <t>Soins infirmiers d'hémodialyse</t>
+  </si>
+  <si>
+    <t>1453</t>
+  </si>
+  <si>
+    <t>Repérage, accompagnement des troubles (neuro)développementaux et comportementaux</t>
+  </si>
+  <si>
+    <t>1454</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi standardisé des commotions cérébrales</t>
+  </si>
+  <si>
+    <t>1455</t>
+  </si>
+  <si>
+    <t>Surveillance et administration de traitement hémophilique</t>
+  </si>
+  <si>
+    <t>1456</t>
+  </si>
+  <si>
+    <t>Surveillance infirmière et remplissage de pompe à morphine</t>
+  </si>
+  <si>
+    <t>1457</t>
+  </si>
+  <si>
+    <t>Visite à domicile infirmière puéricultrice post-natale</t>
+  </si>
+  <si>
+    <t>1458</t>
+  </si>
+  <si>
+    <t>Exploration vasculaire d'effort maximum chez le sportif</t>
+  </si>
+  <si>
+    <t>1459</t>
+  </si>
+  <si>
+    <t>Laximétrie dynamique automatisée du genou (LDA)</t>
+  </si>
+  <si>
+    <t>1460</t>
+  </si>
+  <si>
+    <t>Pressothérapie</t>
   </si>
 </sst>
 </file>
@@ -9687,7 +9909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1427"/>
+  <dimension ref="A1:D1460"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -26950,29 +27172,33 @@
       <c r="C1401" t="s" s="2">
         <v>3047</v>
       </c>
-      <c r="D1401" s="2"/>
+      <c r="D1401" t="s" s="2">
+        <v>3048</v>
+      </c>
     </row>
     <row r="1402">
       <c r="A1402" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1402" t="s" s="2">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="C1402" t="s" s="2">
-        <v>3049</v>
-      </c>
-      <c r="D1402" s="2"/>
+        <v>3050</v>
+      </c>
+      <c r="D1402" t="s" s="2">
+        <v>3051</v>
+      </c>
     </row>
     <row r="1403">
       <c r="A1403" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1403" t="s" s="2">
-        <v>3050</v>
+        <v>3052</v>
       </c>
       <c r="C1403" t="s" s="2">
-        <v>3051</v>
+        <v>3053</v>
       </c>
       <c r="D1403" s="2"/>
     </row>
@@ -26981,10 +27207,10 @@
         <v>49</v>
       </c>
       <c r="B1404" t="s" s="2">
-        <v>3052</v>
+        <v>3054</v>
       </c>
       <c r="C1404" t="s" s="2">
-        <v>3053</v>
+        <v>3055</v>
       </c>
       <c r="D1404" s="2"/>
     </row>
@@ -26993,22 +27219,24 @@
         <v>49</v>
       </c>
       <c r="B1405" t="s" s="2">
-        <v>3054</v>
+        <v>3056</v>
       </c>
       <c r="C1405" t="s" s="2">
-        <v>3055</v>
-      </c>
-      <c r="D1405" s="2"/>
+        <v>3057</v>
+      </c>
+      <c r="D1405" t="s" s="2">
+        <v>3058</v>
+      </c>
     </row>
     <row r="1406">
       <c r="A1406" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1406" t="s" s="2">
-        <v>3056</v>
+        <v>3059</v>
       </c>
       <c r="C1406" t="s" s="2">
-        <v>3057</v>
+        <v>3060</v>
       </c>
       <c r="D1406" s="2"/>
     </row>
@@ -27017,10 +27245,10 @@
         <v>49</v>
       </c>
       <c r="B1407" t="s" s="2">
-        <v>3058</v>
+        <v>3061</v>
       </c>
       <c r="C1407" t="s" s="2">
-        <v>3059</v>
+        <v>3062</v>
       </c>
       <c r="D1407" s="2"/>
     </row>
@@ -27029,10 +27257,10 @@
         <v>49</v>
       </c>
       <c r="B1408" t="s" s="2">
-        <v>3060</v>
+        <v>3063</v>
       </c>
       <c r="C1408" t="s" s="2">
-        <v>3061</v>
+        <v>3064</v>
       </c>
       <c r="D1408" s="2"/>
     </row>
@@ -27041,10 +27269,10 @@
         <v>49</v>
       </c>
       <c r="B1409" t="s" s="2">
-        <v>3062</v>
+        <v>3065</v>
       </c>
       <c r="C1409" t="s" s="2">
-        <v>3063</v>
+        <v>3066</v>
       </c>
       <c r="D1409" s="2"/>
     </row>
@@ -27053,22 +27281,24 @@
         <v>49</v>
       </c>
       <c r="B1410" t="s" s="2">
-        <v>3064</v>
+        <v>3067</v>
       </c>
       <c r="C1410" t="s" s="2">
-        <v>3065</v>
-      </c>
-      <c r="D1410" s="2"/>
+        <v>3068</v>
+      </c>
+      <c r="D1410" t="s" s="2">
+        <v>3069</v>
+      </c>
     </row>
     <row r="1411">
       <c r="A1411" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1411" t="s" s="2">
-        <v>3066</v>
+        <v>3070</v>
       </c>
       <c r="C1411" t="s" s="2">
-        <v>3067</v>
+        <v>3071</v>
       </c>
       <c r="D1411" s="2"/>
     </row>
@@ -27077,10 +27307,10 @@
         <v>49</v>
       </c>
       <c r="B1412" t="s" s="2">
-        <v>3068</v>
+        <v>3072</v>
       </c>
       <c r="C1412" t="s" s="2">
-        <v>3069</v>
+        <v>3073</v>
       </c>
       <c r="D1412" s="2"/>
     </row>
@@ -27089,10 +27319,10 @@
         <v>49</v>
       </c>
       <c r="B1413" t="s" s="2">
-        <v>3070</v>
+        <v>3074</v>
       </c>
       <c r="C1413" t="s" s="2">
-        <v>3071</v>
+        <v>3075</v>
       </c>
       <c r="D1413" s="2"/>
     </row>
@@ -27101,10 +27331,10 @@
         <v>49</v>
       </c>
       <c r="B1414" t="s" s="2">
-        <v>3072</v>
+        <v>3076</v>
       </c>
       <c r="C1414" t="s" s="2">
-        <v>3073</v>
+        <v>3077</v>
       </c>
       <c r="D1414" s="2"/>
     </row>
@@ -27113,10 +27343,10 @@
         <v>49</v>
       </c>
       <c r="B1415" t="s" s="2">
-        <v>3074</v>
+        <v>3078</v>
       </c>
       <c r="C1415" t="s" s="2">
-        <v>3075</v>
+        <v>3079</v>
       </c>
       <c r="D1415" s="2"/>
     </row>
@@ -27125,10 +27355,10 @@
         <v>49</v>
       </c>
       <c r="B1416" t="s" s="2">
-        <v>3076</v>
+        <v>3080</v>
       </c>
       <c r="C1416" t="s" s="2">
-        <v>3077</v>
+        <v>3081</v>
       </c>
       <c r="D1416" s="2"/>
     </row>
@@ -27137,10 +27367,10 @@
         <v>49</v>
       </c>
       <c r="B1417" t="s" s="2">
-        <v>3078</v>
+        <v>3082</v>
       </c>
       <c r="C1417" t="s" s="2">
-        <v>3079</v>
+        <v>3083</v>
       </c>
       <c r="D1417" s="2"/>
     </row>
@@ -27149,10 +27379,10 @@
         <v>49</v>
       </c>
       <c r="B1418" t="s" s="2">
-        <v>3080</v>
+        <v>3084</v>
       </c>
       <c r="C1418" t="s" s="2">
-        <v>3081</v>
+        <v>3085</v>
       </c>
       <c r="D1418" s="2"/>
     </row>
@@ -27161,10 +27391,10 @@
         <v>49</v>
       </c>
       <c r="B1419" t="s" s="2">
-        <v>3082</v>
+        <v>3086</v>
       </c>
       <c r="C1419" t="s" s="2">
-        <v>3083</v>
+        <v>3087</v>
       </c>
       <c r="D1419" s="2"/>
     </row>
@@ -27173,10 +27403,10 @@
         <v>49</v>
       </c>
       <c r="B1420" t="s" s="2">
-        <v>3084</v>
+        <v>3088</v>
       </c>
       <c r="C1420" t="s" s="2">
-        <v>3085</v>
+        <v>3089</v>
       </c>
       <c r="D1420" s="2"/>
     </row>
@@ -27185,10 +27415,10 @@
         <v>49</v>
       </c>
       <c r="B1421" t="s" s="2">
-        <v>3086</v>
+        <v>3090</v>
       </c>
       <c r="C1421" t="s" s="2">
-        <v>3087</v>
+        <v>3091</v>
       </c>
       <c r="D1421" s="2"/>
     </row>
@@ -27197,10 +27427,10 @@
         <v>49</v>
       </c>
       <c r="B1422" t="s" s="2">
-        <v>3088</v>
+        <v>3092</v>
       </c>
       <c r="C1422" t="s" s="2">
-        <v>3089</v>
+        <v>3093</v>
       </c>
       <c r="D1422" s="2"/>
     </row>
@@ -27209,46 +27439,52 @@
         <v>49</v>
       </c>
       <c r="B1423" t="s" s="2">
-        <v>3090</v>
+        <v>3094</v>
       </c>
       <c r="C1423" t="s" s="2">
-        <v>3091</v>
-      </c>
-      <c r="D1423" s="2"/>
+        <v>3095</v>
+      </c>
+      <c r="D1423" t="s" s="2">
+        <v>3096</v>
+      </c>
     </row>
     <row r="1424">
       <c r="A1424" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1424" t="s" s="2">
-        <v>3092</v>
+        <v>3097</v>
       </c>
       <c r="C1424" t="s" s="2">
-        <v>3093</v>
-      </c>
-      <c r="D1424" s="2"/>
+        <v>3098</v>
+      </c>
+      <c r="D1424" t="s" s="2">
+        <v>3099</v>
+      </c>
     </row>
     <row r="1425">
       <c r="A1425" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1425" t="s" s="2">
-        <v>3094</v>
+        <v>3100</v>
       </c>
       <c r="C1425" t="s" s="2">
-        <v>3095</v>
-      </c>
-      <c r="D1425" s="2"/>
+        <v>3101</v>
+      </c>
+      <c r="D1425" t="s" s="2">
+        <v>3102</v>
+      </c>
     </row>
     <row r="1426">
       <c r="A1426" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B1426" t="s" s="2">
-        <v>3096</v>
+        <v>3103</v>
       </c>
       <c r="C1426" t="s" s="2">
-        <v>3097</v>
+        <v>3104</v>
       </c>
       <c r="D1426" s="2"/>
     </row>
@@ -27257,12 +27493,410 @@
         <v>49</v>
       </c>
       <c r="B1427" t="s" s="2">
-        <v>3098</v>
+        <v>3105</v>
       </c>
       <c r="C1427" t="s" s="2">
-        <v>3099</v>
-      </c>
-      <c r="D1427" s="2"/>
+        <v>3106</v>
+      </c>
+      <c r="D1427" t="s" s="2">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1428" t="s" s="2">
+        <v>3108</v>
+      </c>
+      <c r="C1428" t="s" s="2">
+        <v>3109</v>
+      </c>
+      <c r="D1428" s="2"/>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1429" t="s" s="2">
+        <v>3110</v>
+      </c>
+      <c r="C1429" t="s" s="2">
+        <v>3111</v>
+      </c>
+      <c r="D1429" s="2"/>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1430" t="s" s="2">
+        <v>3112</v>
+      </c>
+      <c r="C1430" t="s" s="2">
+        <v>3113</v>
+      </c>
+      <c r="D1430" s="2"/>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1431" t="s" s="2">
+        <v>3114</v>
+      </c>
+      <c r="C1431" t="s" s="2">
+        <v>3115</v>
+      </c>
+      <c r="D1431" s="2"/>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1432" t="s" s="2">
+        <v>3116</v>
+      </c>
+      <c r="C1432" t="s" s="2">
+        <v>3117</v>
+      </c>
+      <c r="D1432" s="2"/>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1433" t="s" s="2">
+        <v>3118</v>
+      </c>
+      <c r="C1433" t="s" s="2">
+        <v>3119</v>
+      </c>
+      <c r="D1433" s="2"/>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1434" t="s" s="2">
+        <v>3120</v>
+      </c>
+      <c r="C1434" t="s" s="2">
+        <v>3121</v>
+      </c>
+      <c r="D1434" s="2"/>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1435" t="s" s="2">
+        <v>3122</v>
+      </c>
+      <c r="C1435" t="s" s="2">
+        <v>3123</v>
+      </c>
+      <c r="D1435" s="2"/>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1436" t="s" s="2">
+        <v>3124</v>
+      </c>
+      <c r="C1436" t="s" s="2">
+        <v>3125</v>
+      </c>
+      <c r="D1436" s="2"/>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1437" t="s" s="2">
+        <v>3126</v>
+      </c>
+      <c r="C1437" t="s" s="2">
+        <v>3127</v>
+      </c>
+      <c r="D1437" s="2"/>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1438" t="s" s="2">
+        <v>3128</v>
+      </c>
+      <c r="C1438" t="s" s="2">
+        <v>3129</v>
+      </c>
+      <c r="D1438" s="2"/>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1439" t="s" s="2">
+        <v>3130</v>
+      </c>
+      <c r="C1439" t="s" s="2">
+        <v>3131</v>
+      </c>
+      <c r="D1439" s="2"/>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1440" t="s" s="2">
+        <v>3132</v>
+      </c>
+      <c r="C1440" t="s" s="2">
+        <v>3133</v>
+      </c>
+      <c r="D1440" s="2"/>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1441" t="s" s="2">
+        <v>3134</v>
+      </c>
+      <c r="C1441" t="s" s="2">
+        <v>3135</v>
+      </c>
+      <c r="D1441" s="2"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1442" t="s" s="2">
+        <v>3136</v>
+      </c>
+      <c r="C1442" t="s" s="2">
+        <v>3137</v>
+      </c>
+      <c r="D1442" s="2"/>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1443" t="s" s="2">
+        <v>3138</v>
+      </c>
+      <c r="C1443" t="s" s="2">
+        <v>3139</v>
+      </c>
+      <c r="D1443" s="2"/>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1444" t="s" s="2">
+        <v>3140</v>
+      </c>
+      <c r="C1444" t="s" s="2">
+        <v>3141</v>
+      </c>
+      <c r="D1444" s="2"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1445" t="s" s="2">
+        <v>3142</v>
+      </c>
+      <c r="C1445" t="s" s="2">
+        <v>3143</v>
+      </c>
+      <c r="D1445" s="2"/>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1446" t="s" s="2">
+        <v>3144</v>
+      </c>
+      <c r="C1446" t="s" s="2">
+        <v>3145</v>
+      </c>
+      <c r="D1446" s="2"/>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1447" t="s" s="2">
+        <v>3146</v>
+      </c>
+      <c r="C1447" t="s" s="2">
+        <v>3147</v>
+      </c>
+      <c r="D1447" s="2"/>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1448" t="s" s="2">
+        <v>3148</v>
+      </c>
+      <c r="C1448" t="s" s="2">
+        <v>3149</v>
+      </c>
+      <c r="D1448" s="2"/>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1449" t="s" s="2">
+        <v>3150</v>
+      </c>
+      <c r="C1449" t="s" s="2">
+        <v>3151</v>
+      </c>
+      <c r="D1449" s="2"/>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1450" t="s" s="2">
+        <v>3152</v>
+      </c>
+      <c r="C1450" t="s" s="2">
+        <v>3153</v>
+      </c>
+      <c r="D1450" s="2"/>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1451" t="s" s="2">
+        <v>3154</v>
+      </c>
+      <c r="C1451" t="s" s="2">
+        <v>3155</v>
+      </c>
+      <c r="D1451" s="2"/>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1452" t="s" s="2">
+        <v>3156</v>
+      </c>
+      <c r="C1452" t="s" s="2">
+        <v>3157</v>
+      </c>
+      <c r="D1452" s="2"/>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1453" t="s" s="2">
+        <v>3158</v>
+      </c>
+      <c r="C1453" t="s" s="2">
+        <v>3159</v>
+      </c>
+      <c r="D1453" s="2"/>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1454" t="s" s="2">
+        <v>3160</v>
+      </c>
+      <c r="C1454" t="s" s="2">
+        <v>3161</v>
+      </c>
+      <c r="D1454" s="2"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1455" t="s" s="2">
+        <v>3162</v>
+      </c>
+      <c r="C1455" t="s" s="2">
+        <v>3163</v>
+      </c>
+      <c r="D1455" s="2"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1456" t="s" s="2">
+        <v>3164</v>
+      </c>
+      <c r="C1456" t="s" s="2">
+        <v>3165</v>
+      </c>
+      <c r="D1456" s="2"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1457" t="s" s="2">
+        <v>3166</v>
+      </c>
+      <c r="C1457" t="s" s="2">
+        <v>3167</v>
+      </c>
+      <c r="D1457" s="2"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1458" t="s" s="2">
+        <v>3168</v>
+      </c>
+      <c r="C1458" t="s" s="2">
+        <v>3169</v>
+      </c>
+      <c r="D1458" s="2"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1459" t="s" s="2">
+        <v>3170</v>
+      </c>
+      <c r="C1459" t="s" s="2">
+        <v>3171</v>
+      </c>
+      <c r="D1459" s="2"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1460" t="s" s="2">
+        <v>3172</v>
+      </c>
+      <c r="C1460" t="s" s="2">
+        <v>3173</v>
+      </c>
+      <c r="D1460" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240628120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4663" uniqueCount="3174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4673" uniqueCount="3181">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20240726120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2024-07-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Acte spécifique</t>
+    <t>Action menée par un ou plusieurs acteur(s) de santé dans le cadre d'une activité. Cet acte peut correspondre à une technique spécialisée ou traduire une expertise discriminante dans le parcours de santé.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -9536,6 +9536,27 @@
   </si>
   <si>
     <t>Pressothérapie</t>
+  </si>
+  <si>
+    <t>1461</t>
+  </si>
+  <si>
+    <t>Diagnostic par télé-AVC</t>
+  </si>
+  <si>
+    <t>Solution de télémédecine qui permet de requérir une expertise neuro-vasculaire aux établissements qui n'en disposent pas, en s'appuyant sur la possibilité de transmettre des images de qualité, et ainsi de réaliser un télédiagnostic, dans le but d'assurer des décisions thérapeutiques (par exemple, la thrombolyse) ou des prises en charges adaptées avec un bénéfice immédiat pour le patient.</t>
+  </si>
+  <si>
+    <t>1462</t>
+  </si>
+  <si>
+    <t>Unité neuro-vasculaire (UNV) de territoire</t>
+  </si>
+  <si>
+    <t>1463</t>
+  </si>
+  <si>
+    <t>Unité neuro-vasculaire (UNV) de recours</t>
   </si>
 </sst>
 </file>
@@ -9909,7 +9930,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1460"/>
+  <dimension ref="A1:D1463"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -27898,6 +27919,44 @@
       </c>
       <c r="D1460" s="2"/>
     </row>
+    <row r="1461">
+      <c r="A1461" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1461" t="s" s="2">
+        <v>3174</v>
+      </c>
+      <c r="C1461" t="s" s="2">
+        <v>3175</v>
+      </c>
+      <c r="D1461" t="s" s="2">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1462" t="s" s="2">
+        <v>3177</v>
+      </c>
+      <c r="C1462" t="s" s="2">
+        <v>3178</v>
+      </c>
+      <c r="D1462" s="2"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1463" t="s" s="2">
+        <v>3179</v>
+      </c>
+      <c r="C1463" t="s" s="2">
+        <v>3180</v>
+      </c>
+      <c r="D1463" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/main/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4731" uniqueCount="3221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4734" uniqueCount="3223">
   <si>
     <t>Property</t>
   </si>
@@ -9517,13 +9517,13 @@
     <t>1455</t>
   </si>
   <si>
-    <t>Surveillance et administration de traitement hémophilique</t>
+    <t>Soins et surveillance d'administration de traitement hémophilique</t>
   </si>
   <si>
     <t>1456</t>
   </si>
   <si>
-    <t>Surveillance infirmière et remplissage de pompe à morphine</t>
+    <t>Soins et surveillance de remplissage de pompe à morphine</t>
   </si>
   <si>
     <t>1457</t>
@@ -9629,6 +9629,12 @@
   </si>
   <si>
     <t>Soins et surveillance des cathéters périnerveux</t>
+  </si>
+  <si>
+    <t>1474</t>
+  </si>
+  <si>
+    <t>Télésoin</t>
   </si>
   <si>
     <t>1475</t>
@@ -10050,7 +10056,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1481"/>
+  <dimension ref="A1:D1482"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -28301,6 +28307,18 @@
       </c>
       <c r="D1481" s="2"/>
     </row>
+    <row r="1482">
+      <c r="A1482" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B1482" t="s" s="2">
+        <v>3221</v>
+      </c>
+      <c r="C1482" t="s" s="2">
+        <v>3222</v>
+      </c>
+      <c r="D1482" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
